--- a/SKU.xlsx
+++ b/SKU.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ข้อมูลในเครื่อง\D - ดาวน์โหลด\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kittiwin\Desktop\web สรุปยอด\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C629A14-1029-46F0-B5D8-0F6D09D1ACDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52199CBD-D1F1-43FA-9AC5-F78C2445C0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,9 +209,6 @@
     <t>99010015</t>
   </si>
   <si>
-    <t>SET แทงใยไหม</t>
-  </si>
-  <si>
     <t>เซท</t>
   </si>
   <si>
@@ -278,9 +275,6 @@
     <t>99010141</t>
   </si>
   <si>
-    <t>TJ-10HD</t>
-  </si>
-  <si>
     <t>99010142</t>
   </si>
   <si>
@@ -290,9 +284,6 @@
     <t>5125728400303</t>
   </si>
   <si>
-    <t>TJ-14HD</t>
-  </si>
-  <si>
     <t>99010144</t>
   </si>
   <si>
@@ -623,9 +614,6 @@
     <t>PLU8821600775</t>
   </si>
   <si>
-    <t>ชุด DIY เกจดิจิตอล+คอปเปอร์THB</t>
-  </si>
-  <si>
     <t>PLU4834266557</t>
   </si>
   <si>
@@ -635,9 +623,6 @@
     <t>PLU5163145361</t>
   </si>
   <si>
-    <t>ชุด DIY เกจน้ำมัน+คอปเปอร์THB</t>
-  </si>
-  <si>
     <t>PLU5114105221</t>
   </si>
   <si>
@@ -1187,27 +1172,15 @@
     <t>99010077</t>
   </si>
   <si>
-    <t>วงกลม L3&lt;52มม&gt;</t>
-  </si>
-  <si>
     <t>99010078</t>
   </si>
   <si>
-    <t>วงกลม MU-00&lt;43มม&gt;</t>
-  </si>
-  <si>
     <t>99010079</t>
   </si>
   <si>
-    <t>วงกลม MU-01&lt;65มม&gt;</t>
-  </si>
-  <si>
     <t>99010080</t>
   </si>
   <si>
-    <t>วงกลม MU-02&lt;78มม&gt;</t>
-  </si>
-  <si>
     <t>PLU8703101071</t>
   </si>
   <si>
@@ -1229,9 +1202,6 @@
     <t>99010081</t>
   </si>
   <si>
-    <t>ศรไส้ไก่50ตัว</t>
-  </si>
-  <si>
     <t>แพ็ค</t>
   </si>
   <si>
@@ -2181,6 +2151,36 @@
   </si>
   <si>
     <t>เลิกขาย</t>
+  </si>
+  <si>
+    <t>วงกลม MU-00</t>
+  </si>
+  <si>
+    <t>วงกลม L3</t>
+  </si>
+  <si>
+    <t>วงกลม MU-01</t>
+  </si>
+  <si>
+    <t>วงกลม MU-02</t>
+  </si>
+  <si>
+    <t>TJ-10</t>
+  </si>
+  <si>
+    <t>TJ-14</t>
+  </si>
+  <si>
+    <t>ชุด DIY เกจน้ำมัน</t>
+  </si>
+  <si>
+    <t>ชุด DIY เกจดิจิตอล</t>
+  </si>
+  <si>
+    <t>เซทแทงใยไหม</t>
+  </si>
+  <si>
+    <t>ศรไส้ไก่ 100ตัว</t>
   </si>
 </sst>
 </file>
@@ -2589,7 +2589,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2618,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F2" s="3">
         <v>200</v>
@@ -2659,7 +2659,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F3" s="3">
         <v>220</v>
@@ -2694,7 +2694,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F4" s="3">
         <v>220</v>
@@ -2729,7 +2729,7 @@
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F5" s="3">
         <v>220</v>
@@ -2764,7 +2764,7 @@
         <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F6" s="3">
         <v>300</v>
@@ -2799,7 +2799,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F7" s="3">
         <v>300</v>
@@ -2834,7 +2834,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F8" s="3">
         <v>300</v>
@@ -2869,7 +2869,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F9" s="3">
         <v>300</v>
@@ -2898,13 +2898,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F10" s="3">
         <v>320</v>
@@ -2933,13 +2933,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F11" s="3">
         <v>320</v>
@@ -2968,13 +2968,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F12" s="3">
         <v>320</v>
@@ -3003,13 +3003,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="F13" s="3">
         <v>320</v>
@@ -3038,13 +3038,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F14" s="3">
         <v>150</v>
@@ -3073,13 +3073,13 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F15" s="3">
         <v>250</v>
@@ -3108,13 +3108,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F16" s="3">
         <v>550</v>
@@ -3140,13 +3140,13 @@
         <v>480</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F17" s="3">
         <v>400</v>
@@ -3175,13 +3175,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F18" s="3">
         <v>500</v>
@@ -3210,13 +3210,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F19" s="3">
         <v>700</v>
@@ -3245,13 +3245,13 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F20" s="3">
         <v>260</v>
@@ -3263,7 +3263,7 @@
         <v>39</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J20" s="3">
         <v>-181</v>
@@ -3280,13 +3280,13 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>385</v>
+        <v>705</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F21" s="3">
         <v>250</v>
@@ -3298,7 +3298,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J21" s="3">
         <v>-90</v>
@@ -3315,13 +3315,13 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>383</v>
+        <v>706</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F22" s="3">
         <v>290</v>
@@ -3333,7 +3333,7 @@
         <v>13</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J22" s="3">
         <v>-89</v>
@@ -3350,13 +3350,13 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>387</v>
+        <v>707</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F23" s="3">
         <v>300</v>
@@ -3368,7 +3368,7 @@
         <v>13</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J23" s="3">
         <v>3</v>
@@ -3385,13 +3385,13 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>389</v>
+        <v>708</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F24" s="3">
         <v>310</v>
@@ -3403,7 +3403,7 @@
         <v>13</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J24" s="3">
         <v>-58</v>
@@ -3420,13 +3420,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F25" s="3">
         <v>660</v>
@@ -3438,7 +3438,7 @@
         <v>13</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J25" s="3">
         <v>3</v>
@@ -3455,13 +3455,13 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F26" s="3">
         <v>750</v>
@@ -3473,7 +3473,7 @@
         <v>13</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J26" s="3">
         <v>-2</v>
@@ -3490,13 +3490,13 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F27" s="3">
         <v>630</v>
@@ -3508,7 +3508,7 @@
         <v>13</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J27" s="3">
         <v>-4</v>
@@ -3525,13 +3525,13 @@
         <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F28" s="3">
         <v>730</v>
@@ -3543,7 +3543,7 @@
         <v>13</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -3566,7 +3566,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="F29" s="3">
         <v>320</v>
@@ -3601,7 +3601,7 @@
         <v>16</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="F30" s="3">
         <v>320</v>
@@ -3636,7 +3636,7 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="F31" s="3">
         <v>320</v>
@@ -3671,7 +3671,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="F32" s="3">
         <v>320</v>
@@ -3706,7 +3706,7 @@
         <v>22</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="F33" s="3">
         <v>320</v>
@@ -3735,13 +3735,13 @@
         <v>33</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F34" s="3">
         <v>320</v>
@@ -3770,13 +3770,13 @@
         <v>34</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F35" s="3">
         <v>200</v>
@@ -3805,13 +3805,13 @@
         <v>35</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F36" s="3">
         <v>200</v>
@@ -3840,13 +3840,13 @@
         <v>36</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F37" s="3">
         <v>350</v>
@@ -3875,13 +3875,13 @@
         <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F38" s="3">
         <v>400</v>
@@ -3910,13 +3910,13 @@
         <v>38</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>80</v>
+        <v>709</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F39" s="3">
         <v>350</v>
@@ -3945,13 +3945,13 @@
         <v>39</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F40" s="3">
         <v>350</v>
@@ -3980,13 +3980,13 @@
         <v>40</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>84</v>
+        <v>710</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F41" s="3">
         <v>350</v>
@@ -4015,13 +4015,13 @@
         <v>41</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F42" s="3">
         <v>35</v>
@@ -4050,13 +4050,13 @@
         <v>42</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F43" s="3">
         <v>40</v>
@@ -4085,13 +4085,13 @@
         <v>43</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F44" s="3">
         <v>45</v>
@@ -4120,13 +4120,13 @@
         <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="F45" s="3">
         <v>27000</v>
@@ -4155,13 +4155,13 @@
         <v>45</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="F46" s="3">
         <v>9000</v>
@@ -4190,13 +4190,13 @@
         <v>46</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>199</v>
+        <v>711</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F47" s="3">
         <v>500</v>
@@ -4225,13 +4225,13 @@
         <v>47</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>195</v>
+        <v>712</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F48" s="3">
         <v>530</v>
@@ -4260,13 +4260,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F49" s="3">
         <v>400</v>
@@ -4295,13 +4295,13 @@
         <v>49</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F50" s="3">
         <v>430</v>
@@ -4330,13 +4330,13 @@
         <v>50</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F51" s="3">
         <v>220</v>
@@ -4365,13 +4365,13 @@
         <v>51</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F52" s="3">
         <v>250</v>
@@ -4400,13 +4400,13 @@
         <v>52</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F53" s="3">
         <v>60</v>
@@ -4435,13 +4435,13 @@
         <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F54" s="3">
         <v>30</v>
@@ -4470,13 +4470,13 @@
         <v>54</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F55" s="3">
         <v>30</v>
@@ -4505,13 +4505,13 @@
         <v>55</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F56" s="3">
         <v>60</v>
@@ -4540,13 +4540,13 @@
         <v>56</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F57" s="3">
         <v>170</v>
@@ -4578,10 +4578,10 @@
         <v>56</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>57</v>
+        <v>713</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -4590,7 +4590,7 @@
         <v>50</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>14</v>
@@ -4610,13 +4610,13 @@
         <v>58</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F59" s="3">
         <v>250</v>
@@ -4625,7 +4625,7 @@
         <v>67</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>14</v>
@@ -4645,13 +4645,13 @@
         <v>59</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F60" s="3">
         <v>450</v>
@@ -4660,7 +4660,7 @@
         <v>80</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>14</v>
@@ -4680,13 +4680,13 @@
         <v>60</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F61" s="3">
         <v>250</v>
@@ -4715,13 +4715,13 @@
         <v>61</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F62" s="3">
         <v>250</v>
@@ -4750,13 +4750,13 @@
         <v>62</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="F63" s="3">
         <v>900</v>
@@ -4785,13 +4785,13 @@
         <v>63</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="F64" s="3">
         <v>220</v>
@@ -4820,13 +4820,13 @@
         <v>64</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="F65" s="3">
         <v>160</v>
@@ -4835,7 +4835,7 @@
         <v>350.26</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>14</v>
@@ -4855,13 +4855,13 @@
         <v>65</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="F66" s="3">
         <v>300</v>
@@ -4890,13 +4890,13 @@
         <v>66</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="F67" s="3">
         <v>10</v>
@@ -4925,13 +4925,13 @@
         <v>67</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="F68" s="3">
         <v>150</v>
@@ -4960,13 +4960,13 @@
         <v>68</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="F69" s="3">
         <v>20</v>
@@ -4995,13 +4995,13 @@
         <v>69</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F70" s="3">
         <v>360</v>
@@ -5030,13 +5030,13 @@
         <v>70</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F71" s="3">
         <v>220</v>
@@ -5045,7 +5045,7 @@
         <v>160</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>14</v>
@@ -5065,13 +5065,13 @@
         <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F72" s="3">
         <v>320</v>
@@ -5080,7 +5080,7 @@
         <v>260</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>14</v>
@@ -5100,13 +5100,13 @@
         <v>72</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F73" s="3">
         <v>370</v>
@@ -5115,7 +5115,7 @@
         <v>260</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>14</v>
@@ -5135,22 +5135,22 @@
         <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>397</v>
+        <v>714</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F74" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G74" s="3">
         <v>15</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>14</v>
@@ -5170,13 +5170,13 @@
         <v>74</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F75" s="3">
         <v>10</v>
@@ -5205,13 +5205,13 @@
         <v>75</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F76" s="3">
         <v>20</v>
@@ -5240,13 +5240,13 @@
         <v>76</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F77" s="3">
         <v>250</v>
@@ -5275,13 +5275,13 @@
         <v>77</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F78" s="3">
         <v>100</v>
@@ -5310,13 +5310,13 @@
         <v>78</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F79" s="3">
         <v>25</v>
@@ -5345,13 +5345,13 @@
         <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F80" s="3">
         <v>15</v>
@@ -5380,13 +5380,13 @@
         <v>80</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F81" s="3">
         <v>10</v>
@@ -5415,13 +5415,13 @@
         <v>81</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F82" s="3">
         <v>220</v>
@@ -5450,13 +5450,13 @@
         <v>82</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F83" s="3">
         <v>20</v>
@@ -5491,7 +5491,7 @@
         <v>38</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F84" s="3">
         <v>150</v>
@@ -5520,13 +5520,13 @@
         <v>84</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F85" s="3">
         <v>150</v>
@@ -5535,7 +5535,7 @@
         <v>75</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>14</v>
@@ -5555,13 +5555,13 @@
         <v>85</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F86" s="3">
         <v>120</v>
@@ -5590,13 +5590,13 @@
         <v>86</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F87" s="3">
         <v>250</v>
@@ -5605,7 +5605,7 @@
         <v>40</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>14</v>
@@ -5625,13 +5625,13 @@
         <v>87</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F88" s="3">
         <v>100</v>
@@ -5660,13 +5660,13 @@
         <v>87</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F89" s="3">
         <v>100</v>
@@ -5695,13 +5695,13 @@
         <v>88</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F90" s="3">
         <v>100</v>
@@ -5730,13 +5730,13 @@
         <v>88</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F91" s="3">
         <v>100</v>
@@ -5765,13 +5765,13 @@
         <v>89</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F92" s="3">
         <v>100</v>
@@ -5800,13 +5800,13 @@
         <v>89</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F93" s="3">
         <v>100</v>
@@ -5835,13 +5835,13 @@
         <v>90</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F94" s="3">
         <v>350</v>
@@ -5870,13 +5870,13 @@
         <v>91</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F95" s="3">
         <v>350</v>
@@ -5905,13 +5905,13 @@
         <v>92</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F96" s="3">
         <v>350</v>
@@ -5940,13 +5940,13 @@
         <v>93</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F97" s="3">
         <v>350</v>
@@ -5975,13 +5975,13 @@
         <v>94</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F98" s="3">
         <v>350</v>
@@ -6010,13 +6010,13 @@
         <v>95</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F99" s="3">
         <v>350</v>
@@ -6045,13 +6045,13 @@
         <v>96</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F100" s="3">
         <v>350</v>
@@ -6080,13 +6080,13 @@
         <v>97</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F101" s="3">
         <v>350</v>
@@ -6115,13 +6115,13 @@
         <v>98</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F102" s="3">
         <v>350</v>
@@ -6150,13 +6150,13 @@
         <v>99</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F103" s="3">
         <v>350</v>
@@ -6185,13 +6185,13 @@
         <v>100</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F104" s="3">
         <v>350</v>
@@ -6220,13 +6220,13 @@
         <v>101</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F105" s="3">
         <v>350</v>
@@ -6255,13 +6255,13 @@
         <v>102</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F106" s="3">
         <v>350</v>
@@ -6290,13 +6290,13 @@
         <v>103</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F107" s="3">
         <v>350</v>
@@ -6305,7 +6305,7 @@
         <v>75</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>14</v>
@@ -6325,13 +6325,13 @@
         <v>104</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F108" s="3">
         <v>350</v>
@@ -6360,13 +6360,13 @@
         <v>105</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="F109" s="3">
         <v>350</v>
@@ -6395,13 +6395,13 @@
         <v>106</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F110" s="3">
         <v>20</v>
@@ -6430,13 +6430,13 @@
         <v>107</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F111" s="3">
         <v>20</v>
@@ -6465,13 +6465,13 @@
         <v>108</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F112" s="3">
         <v>25</v>
@@ -6500,13 +6500,13 @@
         <v>109</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F113" s="3">
         <v>25</v>
@@ -6535,13 +6535,13 @@
         <v>110</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F114" s="3">
         <v>10</v>
@@ -6570,13 +6570,13 @@
         <v>111</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F115" s="3">
         <v>10</v>
@@ -6605,13 +6605,13 @@
         <v>112</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F116" s="3">
         <v>10</v>
@@ -6640,13 +6640,13 @@
         <v>113</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F117" s="3">
         <v>10</v>
@@ -6675,13 +6675,13 @@
         <v>114</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F118" s="3">
         <v>10</v>
@@ -6710,13 +6710,13 @@
         <v>115</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F119" s="3">
         <v>60</v>
@@ -6725,7 +6725,7 @@
         <v>45</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>14</v>
@@ -6745,13 +6745,13 @@
         <v>116</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F120" s="3">
         <v>60</v>
@@ -6760,7 +6760,7 @@
         <v>45</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>14</v>
@@ -6780,13 +6780,13 @@
         <v>117</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F121" s="3">
         <v>150</v>
@@ -6795,7 +6795,7 @@
         <v>105</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>14</v>
@@ -6815,13 +6815,13 @@
         <v>118</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F122" s="3">
         <v>150</v>
@@ -6830,7 +6830,7 @@
         <v>105</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>14</v>
@@ -6850,13 +6850,13 @@
         <v>119</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F123" s="3">
         <v>150</v>
@@ -6865,7 +6865,7 @@
         <v>105</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>14</v>
@@ -6885,13 +6885,13 @@
         <v>120</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F124" s="3">
         <v>150</v>
@@ -6900,7 +6900,7 @@
         <v>105</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>14</v>
@@ -6920,13 +6920,13 @@
         <v>121</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F125" s="3">
         <v>115</v>
@@ -6935,7 +6935,7 @@
         <v>76</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>14</v>
@@ -6955,13 +6955,13 @@
         <v>122</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F126" s="3">
         <v>115</v>
@@ -6970,7 +6970,7 @@
         <v>76</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>14</v>
@@ -6990,13 +6990,13 @@
         <v>123</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F127" s="3">
         <v>105</v>
@@ -7005,7 +7005,7 @@
         <v>71</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>14</v>
@@ -7025,13 +7025,13 @@
         <v>124</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F128" s="3">
         <v>105</v>
@@ -7040,7 +7040,7 @@
         <v>71</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>14</v>
@@ -7060,13 +7060,13 @@
         <v>125</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F129" s="3">
         <v>105</v>
@@ -7075,7 +7075,7 @@
         <v>68</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>14</v>
@@ -7095,13 +7095,13 @@
         <v>126</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F130" s="3">
         <v>105</v>
@@ -7110,7 +7110,7 @@
         <v>71</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>14</v>
@@ -7130,13 +7130,13 @@
         <v>127</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F131" s="3">
         <v>105</v>
@@ -7145,7 +7145,7 @@
         <v>63</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>14</v>
@@ -7165,13 +7165,13 @@
         <v>128</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F132" s="3">
         <v>105</v>
@@ -7180,7 +7180,7 @@
         <v>63</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>14</v>
@@ -7200,13 +7200,13 @@
         <v>129</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F133" s="3">
         <v>105</v>
@@ -7215,7 +7215,7 @@
         <v>71</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>14</v>
@@ -7235,13 +7235,13 @@
         <v>130</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F134" s="3">
         <v>105</v>
@@ -7250,7 +7250,7 @@
         <v>71</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>14</v>
@@ -7270,13 +7270,13 @@
         <v>131</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F135" s="3">
         <v>105</v>
@@ -7285,7 +7285,7 @@
         <v>63</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>14</v>
@@ -7305,13 +7305,13 @@
         <v>132</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F136" s="3">
         <v>105</v>
@@ -7320,7 +7320,7 @@
         <v>63</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>14</v>
@@ -7340,13 +7340,13 @@
         <v>133</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F137" s="3">
         <v>105</v>
@@ -7355,7 +7355,7 @@
         <v>68</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>14</v>
@@ -7375,13 +7375,13 @@
         <v>134</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F138" s="3">
         <v>105</v>
@@ -7390,7 +7390,7 @@
         <v>68</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>14</v>
@@ -7410,13 +7410,13 @@
         <v>135</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F139" s="3">
         <v>105</v>
@@ -7425,7 +7425,7 @@
         <v>68</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>14</v>
@@ -7445,13 +7445,13 @@
         <v>136</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F140" s="3">
         <v>105</v>
@@ -7460,7 +7460,7 @@
         <v>68</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>14</v>
@@ -7480,13 +7480,13 @@
         <v>137</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F141" s="3">
         <v>105</v>
@@ -7495,7 +7495,7 @@
         <v>68</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>14</v>
@@ -7515,13 +7515,13 @@
         <v>138</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F142" s="3">
         <v>105</v>
@@ -7530,7 +7530,7 @@
         <v>68</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>14</v>
@@ -7550,13 +7550,13 @@
         <v>139</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F143" s="3">
         <v>105</v>
@@ -7565,7 +7565,7 @@
         <v>68</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>14</v>
@@ -7585,13 +7585,13 @@
         <v>140</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="F144" s="3">
         <v>105</v>
@@ -7600,7 +7600,7 @@
         <v>68</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>14</v>
@@ -7620,13 +7620,13 @@
         <v>141</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F145" s="3">
         <v>135</v>
@@ -7635,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>14</v>
@@ -7655,13 +7655,13 @@
         <v>142</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F146" s="3">
         <v>160</v>
@@ -7670,7 +7670,7 @@
         <v>120</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>14</v>
@@ -7690,13 +7690,13 @@
         <v>143</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F147" s="3">
         <v>260</v>
@@ -7705,7 +7705,7 @@
         <v>200</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>14</v>
@@ -7725,13 +7725,13 @@
         <v>144</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F148" s="3">
         <v>300</v>
@@ -7740,7 +7740,7 @@
         <v>230</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>14</v>
@@ -7760,13 +7760,13 @@
         <v>145</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F149" s="3">
         <v>260</v>
@@ -7775,7 +7775,7 @@
         <v>200</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>14</v>
@@ -7795,13 +7795,13 @@
         <v>146</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F150" s="3">
         <v>310</v>
@@ -7810,7 +7810,7 @@
         <v>250</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I150" s="2" t="s">
         <v>14</v>
@@ -7830,13 +7830,13 @@
         <v>147</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F151" s="3">
         <v>360</v>
@@ -7845,7 +7845,7 @@
         <v>280</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>14</v>
@@ -7865,13 +7865,13 @@
         <v>148</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F152" s="3">
         <v>350</v>
@@ -7900,13 +7900,13 @@
         <v>149</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F153" s="3">
         <v>500</v>
@@ -7935,13 +7935,13 @@
         <v>150</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F154" s="3">
         <v>560</v>
@@ -7970,13 +7970,13 @@
         <v>151</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="F155" s="3">
         <v>160</v>
@@ -8005,13 +8005,13 @@
         <v>152</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="F156" s="3">
         <v>180</v>
@@ -8040,13 +8040,13 @@
         <v>153</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="F157" s="3">
         <v>180</v>
@@ -8075,13 +8075,13 @@
         <v>154</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="F158" s="3">
         <v>220</v>
@@ -8110,13 +8110,13 @@
         <v>155</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="F159" s="3">
         <v>300</v>
@@ -8145,13 +8145,13 @@
         <v>156</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="F160" s="3">
         <v>100</v>
@@ -8180,13 +8180,13 @@
         <v>157</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="F161" s="3">
         <v>100</v>
@@ -8215,13 +8215,13 @@
         <v>158</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="F162" s="3">
         <v>100</v>
@@ -8250,13 +8250,13 @@
         <v>159</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="F163" s="3">
         <v>100</v>
@@ -8285,13 +8285,13 @@
         <v>160</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="F164" s="3">
         <v>2000</v>
@@ -8320,13 +8320,13 @@
         <v>161</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="F165" s="3">
         <v>1840</v>
@@ -8355,13 +8355,13 @@
         <v>162</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="F166" s="3">
         <v>1000</v>
@@ -8390,13 +8390,13 @@
         <v>163</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="F167" s="3">
         <v>550</v>
@@ -8425,13 +8425,13 @@
         <v>164</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="F168" s="3">
         <v>150</v>
@@ -8460,13 +8460,13 @@
         <v>165</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="F169" s="3">
         <v>80</v>
@@ -8495,13 +8495,13 @@
         <v>166</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="F170" s="3">
         <v>100</v>
@@ -8530,13 +8530,13 @@
         <v>167</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="F171" s="3">
         <v>120</v>
@@ -8565,13 +8565,13 @@
         <v>168</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="F172" s="3">
         <v>180</v>
@@ -8600,13 +8600,13 @@
         <v>169</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="F173" s="3">
         <v>200</v>
@@ -8635,13 +8635,13 @@
         <v>170</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F174" s="3">
         <v>550</v>
@@ -8650,7 +8650,7 @@
         <v>257</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I174" s="2" t="s">
         <v>14</v>
@@ -8670,13 +8670,13 @@
         <v>171</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F175" s="3">
         <v>200</v>
@@ -8705,13 +8705,13 @@
         <v>172</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F176" s="3">
         <v>50</v>
@@ -8740,13 +8740,13 @@
         <v>173</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F177" s="3">
         <v>50</v>
@@ -8775,13 +8775,13 @@
         <v>174</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F178" s="3">
         <v>25</v>
@@ -8810,13 +8810,13 @@
         <v>175</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F179" s="3">
         <v>25</v>
@@ -8845,13 +8845,13 @@
         <v>176</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="F180" s="3">
         <v>200</v>
@@ -8880,13 +8880,13 @@
         <v>177</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="F181" s="3">
         <v>100</v>
@@ -8915,13 +8915,13 @@
         <v>178</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F182" s="3">
         <v>2000</v>
@@ -8950,13 +8950,13 @@
         <v>179</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F183" s="3">
         <v>890</v>
@@ -8985,13 +8985,13 @@
         <v>180</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F184" s="3">
         <v>1400</v>
@@ -9000,7 +9000,7 @@
         <v>1000</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I184" s="2" t="s">
         <v>14</v>
@@ -9020,13 +9020,13 @@
         <v>181</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F185" s="3">
         <v>450</v>
@@ -9055,13 +9055,13 @@
         <v>182</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F186" s="3">
         <v>50</v>
@@ -9090,13 +9090,13 @@
         <v>183</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F187" s="3">
         <v>150</v>
@@ -9125,13 +9125,13 @@
         <v>184</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F188" s="3">
         <v>230</v>
@@ -9160,13 +9160,13 @@
         <v>185</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F189" s="3">
         <v>250</v>
@@ -9195,13 +9195,13 @@
         <v>186</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F190" s="3">
         <v>300</v>
@@ -9230,13 +9230,13 @@
         <v>187</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F191" s="3">
         <v>350</v>
@@ -9265,13 +9265,13 @@
         <v>188</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F192" s="3">
         <v>420</v>
@@ -9300,13 +9300,13 @@
         <v>189</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F193" s="3">
         <v>25</v>
@@ -9335,13 +9335,13 @@
         <v>190</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F194" s="3">
         <v>25</v>
@@ -9370,13 +9370,13 @@
         <v>191</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F195" s="3">
         <v>25</v>
@@ -9405,13 +9405,13 @@
         <v>192</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F196" s="3">
         <v>10</v>
@@ -9440,13 +9440,13 @@
         <v>193</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F197" s="3">
         <v>10</v>
@@ -9475,13 +9475,13 @@
         <v>194</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F198" s="3">
         <v>10</v>
@@ -9510,13 +9510,13 @@
         <v>195</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F199" s="3">
         <v>120</v>
@@ -9545,13 +9545,13 @@
         <v>196</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F200" s="3">
         <v>120</v>
@@ -9580,13 +9580,13 @@
         <v>197</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F201" s="3">
         <v>120</v>
@@ -9615,13 +9615,13 @@
         <v>198</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F202" s="3">
         <v>50</v>
@@ -9650,13 +9650,13 @@
         <v>199</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F203" s="3">
         <v>50</v>
@@ -9685,13 +9685,13 @@
         <v>200</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F204" s="3">
         <v>50</v>
@@ -9720,13 +9720,13 @@
         <v>201</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F205" s="3">
         <v>120</v>
@@ -9744,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="206" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9755,13 +9755,13 @@
         <v>202</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F206" s="3">
         <v>120</v>
@@ -9779,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="207" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9790,13 +9790,13 @@
         <v>203</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F207" s="3">
         <v>120</v>
@@ -9814,7 +9814,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="208" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9825,13 +9825,13 @@
         <v>204</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F208" s="3">
         <v>50</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="209" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9860,13 +9860,13 @@
         <v>205</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F209" s="3">
         <v>50</v>
@@ -9884,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="210" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9895,13 +9895,13 @@
         <v>206</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F210" s="3">
         <v>50</v>
@@ -9919,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="211" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9930,13 +9930,13 @@
         <v>207</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F211" s="3">
         <v>25</v>
@@ -9965,13 +9965,13 @@
         <v>208</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F212" s="3">
         <v>120</v>
@@ -10000,13 +10000,13 @@
         <v>209</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F213" s="3">
         <v>120</v>
@@ -10024,7 +10024,7 @@
         <v>9</v>
       </c>
       <c r="K213" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="214" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10035,13 +10035,13 @@
         <v>210</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F214" s="3">
         <v>120</v>
@@ -10059,7 +10059,7 @@
         <v>4</v>
       </c>
       <c r="K214" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="215" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10070,13 +10070,13 @@
         <v>211</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F215" s="3">
         <v>10</v>
@@ -10105,13 +10105,13 @@
         <v>212</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F216" s="3">
         <v>50</v>
@@ -10140,13 +10140,13 @@
         <v>213</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F217" s="3">
         <v>50</v>
@@ -10164,7 +10164,7 @@
         <v>7</v>
       </c>
       <c r="K217" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="218" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10175,13 +10175,13 @@
         <v>214</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F218" s="3">
         <v>50</v>
@@ -10199,7 +10199,7 @@
         <v>8</v>
       </c>
       <c r="K218" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="219" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10210,13 +10210,13 @@
         <v>215</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F219" s="3">
         <v>120</v>
@@ -10234,7 +10234,7 @@
         <v>9</v>
       </c>
       <c r="K219" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="220" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10245,13 +10245,13 @@
         <v>216</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F220" s="3">
         <v>120</v>
@@ -10269,7 +10269,7 @@
         <v>10</v>
       </c>
       <c r="K220" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="221" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10280,13 +10280,13 @@
         <v>217</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F221" s="3">
         <v>120</v>
@@ -10304,7 +10304,7 @@
         <v>5</v>
       </c>
       <c r="K221" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="222" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10315,13 +10315,13 @@
         <v>218</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F222" s="3">
         <v>50</v>
@@ -10339,7 +10339,7 @@
         <v>8</v>
       </c>
       <c r="K222" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="223" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10350,13 +10350,13 @@
         <v>219</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F223" s="3">
         <v>50</v>
@@ -10374,7 +10374,7 @@
         <v>10</v>
       </c>
       <c r="K223" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="224" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10385,13 +10385,13 @@
         <v>220</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F224" s="3">
         <v>50</v>
@@ -10409,7 +10409,7 @@
         <v>10</v>
       </c>
       <c r="K224" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="225" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10420,13 +10420,13 @@
         <v>221</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="F225" s="3">
         <v>30</v>
@@ -10455,13 +10455,13 @@
         <v>222</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F226" s="3">
         <v>100</v>
@@ -10490,13 +10490,13 @@
         <v>223</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="E227" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F227" s="3">
         <v>60</v>
@@ -10525,13 +10525,13 @@
         <v>224</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D228" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="E228" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F228" s="3">
         <v>80</v>
@@ -10560,13 +10560,13 @@
         <v>225</v>
       </c>
       <c r="C229" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E229" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F229" s="3">
         <v>60</v>
@@ -10595,13 +10595,13 @@
         <v>226</v>
       </c>
       <c r="C230" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="E230" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F230" s="3">
         <v>50</v>
@@ -10636,7 +10636,7 @@
         <v>50</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F231" s="3">
         <v>37</v>
@@ -10671,7 +10671,7 @@
         <v>41</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F232" s="3">
         <v>18.5</v>
@@ -10700,13 +10700,13 @@
         <v>282</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="E233" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="F233" s="3">
         <v>10</v>
@@ -10735,13 +10735,13 @@
         <v>283</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="E234" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="F234" s="3">
         <v>15</v>
@@ -10770,13 +10770,13 @@
         <v>284</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D235" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="E235" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="F235" s="3">
         <v>20</v>
@@ -10805,13 +10805,13 @@
         <v>285</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D236" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="E236" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="F236" s="3">
         <v>30</v>
@@ -10840,13 +10840,13 @@
         <v>286</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D237" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="E237" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="F237" s="3">
         <v>40</v>
@@ -10872,13 +10872,13 @@
         <v>788</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="F238" s="3">
         <v>15</v>
@@ -10904,13 +10904,13 @@
         <v>789</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="F239" s="3">
         <v>15</v>
@@ -10936,13 +10936,13 @@
         <v>790</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="F240" s="3">
         <v>15</v>
@@ -10971,13 +10971,13 @@
         <v>229</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="F241" s="3">
         <v>60</v>
@@ -11006,13 +11006,13 @@
         <v>230</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="F242" s="3">
         <v>60</v>
@@ -11041,13 +11041,13 @@
         <v>231</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="F243" s="3">
         <v>180</v>
@@ -11076,13 +11076,13 @@
         <v>232</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="F244" s="3">
         <v>60</v>
@@ -11111,13 +11111,13 @@
         <v>233</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F245" s="3">
         <v>130</v>
@@ -11146,13 +11146,13 @@
         <v>234</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F246" s="3">
         <v>200</v>
@@ -11181,13 +11181,13 @@
         <v>235</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F247" s="3">
         <v>220</v>
@@ -11216,13 +11216,13 @@
         <v>236</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F248" s="3">
         <v>300</v>
@@ -11251,13 +11251,13 @@
         <v>237</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F249" s="3">
         <v>320</v>
@@ -11286,13 +11286,13 @@
         <v>238</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F250" s="3">
         <v>200</v>
@@ -11321,13 +11321,13 @@
         <v>239</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F251" s="3">
         <v>250</v>
@@ -11356,13 +11356,13 @@
         <v>240</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F252" s="3">
         <v>30</v>
@@ -11371,7 +11371,7 @@
         <v>3.5</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I252" s="2" t="s">
         <v>14</v>
@@ -11391,13 +11391,13 @@
         <v>241</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F253" s="3">
         <v>250</v>
@@ -11426,13 +11426,13 @@
         <v>242</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F254" s="3">
         <v>320</v>
@@ -11461,13 +11461,13 @@
         <v>243</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F255" s="3">
         <v>200</v>
@@ -11496,13 +11496,13 @@
         <v>244</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F256" s="3">
         <v>150</v>
@@ -11531,13 +11531,13 @@
         <v>245</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F257" s="3">
         <v>300</v>
@@ -11566,13 +11566,13 @@
         <v>246</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F258" s="3">
         <v>750</v>
@@ -11601,13 +11601,13 @@
         <v>247</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F259" s="3">
         <v>750</v>
@@ -11636,13 +11636,13 @@
         <v>248</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="F260" s="3">
         <v>120</v>
@@ -11671,13 +11671,13 @@
         <v>249</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="F261" s="3">
         <v>70</v>
@@ -11686,7 +11686,7 @@
         <v>30</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I261" s="2" t="s">
         <v>14</v>
@@ -11706,13 +11706,13 @@
         <v>250</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="F262" s="3">
         <v>120</v>
@@ -11741,13 +11741,13 @@
         <v>251</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="F263" s="3">
         <v>200</v>
@@ -11776,13 +11776,13 @@
         <v>252</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="F264" s="3">
         <v>12</v>
@@ -11811,13 +11811,13 @@
         <v>253</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="F265" s="3">
         <v>12</v>
@@ -11846,13 +11846,13 @@
         <v>254</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="F266" s="3">
         <v>50</v>
@@ -11881,13 +11881,13 @@
         <v>255</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="F267" s="3">
         <v>80</v>
@@ -11916,13 +11916,13 @@
         <v>256</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="F268" s="3">
         <v>70</v>
@@ -11951,13 +11951,13 @@
         <v>257</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F269" s="3">
         <v>380</v>
@@ -11966,7 +11966,7 @@
         <v>260</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I269" s="2" t="s">
         <v>14</v>
@@ -11986,13 +11986,13 @@
         <v>258</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F270" s="3">
         <v>330</v>
@@ -12001,7 +12001,7 @@
         <v>142</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I270" s="2" t="s">
         <v>14</v>
@@ -12021,13 +12021,13 @@
         <v>259</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F271" s="3">
         <v>380</v>
@@ -12036,7 +12036,7 @@
         <v>235</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I271" s="2" t="s">
         <v>14</v>
@@ -12056,13 +12056,13 @@
         <v>260</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F272" s="3">
         <v>380</v>
@@ -12071,7 +12071,7 @@
         <v>235</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I272" s="2" t="s">
         <v>14</v>
@@ -12091,13 +12091,13 @@
         <v>261</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F273" s="3">
         <v>15</v>
@@ -12126,13 +12126,13 @@
         <v>262</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F274" s="3">
         <v>10</v>
@@ -12161,13 +12161,13 @@
         <v>263</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F275" s="3">
         <v>10</v>
@@ -12196,13 +12196,13 @@
         <v>264</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F276" s="3">
         <v>10</v>
@@ -12231,13 +12231,13 @@
         <v>265</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F277" s="3">
         <v>10</v>
@@ -12266,13 +12266,13 @@
         <v>266</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F278" s="3">
         <v>5</v>
@@ -12301,13 +12301,13 @@
         <v>267</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F279" s="3">
         <v>5</v>
@@ -12336,13 +12336,13 @@
         <v>268</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F280" s="3">
         <v>5</v>
@@ -12371,13 +12371,13 @@
         <v>269</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F281" s="3">
         <v>15</v>
@@ -12406,13 +12406,13 @@
         <v>270</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F282" s="3">
         <v>15</v>
@@ -12441,13 +12441,13 @@
         <v>271</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F283" s="3">
         <v>10</v>
@@ -12476,13 +12476,13 @@
         <v>272</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F284" s="3">
         <v>15</v>
@@ -12511,13 +12511,13 @@
         <v>273</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F285" s="3">
         <v>40</v>
@@ -12546,13 +12546,13 @@
         <v>274</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F286" s="3">
         <v>25</v>
@@ -12581,13 +12581,13 @@
         <v>275</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F287" s="3">
         <v>25</v>
@@ -12616,13 +12616,13 @@
         <v>276</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F288" s="3">
         <v>50</v>
@@ -12651,13 +12651,13 @@
         <v>277</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F289" s="3">
         <v>50</v>
@@ -12686,13 +12686,13 @@
         <v>278</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F290" s="3">
         <v>50</v>
@@ -12721,13 +12721,13 @@
         <v>279</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F291" s="3">
         <v>50</v>
@@ -12756,13 +12756,13 @@
         <v>280</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F292" s="3">
         <v>60</v>
@@ -12791,13 +12791,13 @@
         <v>281</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F293" s="3">
         <v>60</v>
@@ -12823,7 +12823,7 @@
         <v>319</v>
       </c>
       <c r="B294" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>43</v>
@@ -12832,7 +12832,7 @@
         <v>44</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F294" s="3">
         <v>1850</v>
@@ -12858,7 +12858,7 @@
         <v>320</v>
       </c>
       <c r="B295" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>45</v>
@@ -12867,7 +12867,7 @@
         <v>46</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F295" s="3">
         <v>370</v>
@@ -12893,7 +12893,7 @@
         <v>321</v>
       </c>
       <c r="B296" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>47</v>
@@ -12902,7 +12902,7 @@
         <v>48</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F296" s="3">
         <v>46</v>
@@ -12928,7 +12928,7 @@
         <v>323</v>
       </c>
       <c r="B297" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>51</v>
@@ -12937,7 +12937,7 @@
         <v>52</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F297" s="3">
         <v>31</v>
@@ -12963,7 +12963,7 @@
         <v>324</v>
       </c>
       <c r="B298" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>53</v>
@@ -12972,7 +12972,7 @@
         <v>54</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F298" s="3">
         <v>23.5</v>
@@ -12998,16 +12998,16 @@
         <v>557</v>
       </c>
       <c r="B299" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F299" s="3">
         <v>490</v>
@@ -13033,13 +13033,13 @@
         <v>388</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F300" s="3">
         <v>150</v>
@@ -13065,13 +13065,13 @@
         <v>403</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F301" s="3">
         <v>20</v>
@@ -13097,13 +13097,13 @@
         <v>425</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F302" s="3">
         <v>50</v>
@@ -13129,13 +13129,13 @@
         <v>493</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F303" s="3">
         <v>200</v>
@@ -13161,13 +13161,13 @@
         <v>494</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F304" s="3">
         <v>100</v>
@@ -13193,13 +13193,13 @@
         <v>538</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F305" s="3">
         <v>300</v>
@@ -13208,7 +13208,7 @@
         <v>150</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I305" s="2" t="s">
         <v>14</v>
@@ -13225,13 +13225,13 @@
         <v>609</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F306" s="3">
         <v>0</v>
@@ -13257,13 +13257,13 @@
         <v>611</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F307" s="3">
         <v>1200</v>
@@ -13289,13 +13289,13 @@
         <v>613</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F308" s="3">
         <v>1400</v>
@@ -13321,13 +13321,13 @@
         <v>615</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F309" s="3">
         <v>1400</v>
@@ -13353,13 +13353,13 @@
         <v>617</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F310" s="3">
         <v>1800</v>
@@ -13385,13 +13385,13 @@
         <v>619</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F311" s="3">
         <v>200</v>
@@ -13400,7 +13400,7 @@
         <v>115</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I311" s="2" t="s">
         <v>14</v>
@@ -13417,13 +13417,13 @@
         <v>620</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F312" s="3">
         <v>220</v>
@@ -13432,7 +13432,7 @@
         <v>115</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I312" s="2" t="s">
         <v>14</v>
@@ -13449,13 +13449,13 @@
         <v>621</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F313" s="3">
         <v>245</v>
@@ -13464,7 +13464,7 @@
         <v>135</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I313" s="2" t="s">
         <v>14</v>
@@ -13481,13 +13481,13 @@
         <v>622</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F314" s="3">
         <v>265</v>
@@ -13496,7 +13496,7 @@
         <v>160</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I314" s="2" t="s">
         <v>14</v>
@@ -13513,13 +13513,13 @@
         <v>623</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F315" s="3">
         <v>305</v>
@@ -13528,7 +13528,7 @@
         <v>160</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I315" s="2" t="s">
         <v>14</v>
@@ -13545,13 +13545,13 @@
         <v>754</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F316" s="3">
         <v>990</v>
@@ -13577,13 +13577,13 @@
         <v>755</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F317" s="3">
         <v>890</v>
@@ -13601,7 +13601,7 @@
         <v>-1</v>
       </c>
       <c r="K317" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="318" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13609,13 +13609,13 @@
         <v>778</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F318" s="3">
         <v>400</v>
@@ -13641,13 +13641,13 @@
         <v>779</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F319" s="3">
         <v>350</v>
@@ -13673,13 +13673,13 @@
         <v>791</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F320" s="3">
         <v>15</v>
@@ -13705,13 +13705,13 @@
         <v>838</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F321" s="3">
         <v>50</v>
@@ -13737,13 +13737,13 @@
         <v>839</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F322" s="3">
         <v>5000</v>
@@ -13769,13 +13769,13 @@
         <v>841</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F323" s="3">
         <v>850</v>
@@ -13801,13 +13801,13 @@
         <v>902</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="F324" s="3">
         <v>200</v>
